--- a/data/trans_camb/P16A_n_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A_n_R2-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 9,58</t>
+          <t>-1,41; 10,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 10,63</t>
+          <t>0,22; 11,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,38; 16,72</t>
+          <t>6,03; 16,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 8,96</t>
+          <t>-4,68; 9,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 5,76</t>
+          <t>-7,3; 5,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 15,01</t>
+          <t>2,06; 14,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 8,11</t>
+          <t>-0,57; 8,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 7,15</t>
+          <t>-1,74; 6,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,51; 14,6</t>
+          <t>6,81; 14,44</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 65,34</t>
+          <t>-8,29; 71,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 74,52</t>
+          <t>0,51; 81,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,88; 125,72</t>
+          <t>30,95; 115,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,8; 44,62</t>
+          <t>-18,46; 49,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,06; 29,34</t>
+          <t>-27,16; 27,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,74; 80,88</t>
+          <t>7,51; 75,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 46,53</t>
+          <t>-3,11; 47,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 40,99</t>
+          <t>-7,87; 39,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,76; 87,94</t>
+          <t>32,11; 84,83</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 12,63</t>
+          <t>0,82; 12,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,33; 14,63</t>
+          <t>2,78; 14,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,11; 18,76</t>
+          <t>7,61; 18,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 12,18</t>
+          <t>-2,1; 12,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 7,48</t>
+          <t>-5,2; 7,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,26; 15,31</t>
+          <t>3,63; 15,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 10,28</t>
+          <t>1,1; 9,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 8,99</t>
+          <t>0,7; 8,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,76; 15,13</t>
+          <t>7,14; 14,89</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,2; 107,71</t>
+          <t>4,71; 107,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,01; 125,74</t>
+          <t>15,54; 126,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40,68; 165,24</t>
+          <t>45,7; 169,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 61,57</t>
+          <t>-8,42; 61,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-19,99; 37,19</t>
+          <t>-20,04; 36,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,79; 78,12</t>
+          <t>12,29; 76,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,35; 62,54</t>
+          <t>5,07; 58,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 54,34</t>
+          <t>3,13; 53,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,76; 92,26</t>
+          <t>33,58; 90,73</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,43; 18,51</t>
+          <t>8,65; 18,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,02; 13,97</t>
+          <t>3,55; 13,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 18,39</t>
+          <t>-12,54; 17,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 19,5</t>
+          <t>0,67; 18,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 22,96</t>
+          <t>1,13; 23,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,98; 34,82</t>
+          <t>15,95; 34,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,05; 17,89</t>
+          <t>8,12; 17,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,78; 14,1</t>
+          <t>4,9; 14,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 20,35</t>
+          <t>-7,94; 20,29</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>43,05; 123,87</t>
+          <t>44,13; 121,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,48; 95,2</t>
+          <t>17,55; 90,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-52,61; 113,74</t>
+          <t>-59,32; 106,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,69; 92,56</t>
+          <t>1,35; 86,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,9; 110,39</t>
+          <t>2,55; 105,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45,13; 160,61</t>
+          <t>48,29; 160,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,53; 104,32</t>
+          <t>37,06; 99,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22,85; 80,62</t>
+          <t>22,4; 80,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-43,8; 107,19</t>
+          <t>-37,09; 108,47</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,88; 11,14</t>
+          <t>3,71; 10,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,02; 6,87</t>
+          <t>-0,24; 6,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,87; 16,97</t>
+          <t>9,25; 17,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,3; 12,2</t>
+          <t>2,04; 11,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 5,65</t>
+          <t>-3,61; 5,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,72; 48,71</t>
+          <t>10,78; 45,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,61; 10,27</t>
+          <t>4,75; 10,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 5,12</t>
+          <t>-0,1; 5,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,73; 35,23</t>
+          <t>12,02; 37,68</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,02; 54,26</t>
+          <t>16,45; 54,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,24; 34,37</t>
+          <t>-1,15; 32,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39,13; 86,37</t>
+          <t>38,84; 81,99</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,09; 51,42</t>
+          <t>7,25; 50,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 23,71</t>
+          <t>-12,8; 24,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,15; 206,85</t>
+          <t>39,64; 188,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,67; 46,91</t>
+          <t>19,9; 47,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 23,7</t>
+          <t>-0,36; 23,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>49,03; 159,11</t>
+          <t>50,43; 169,03</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,18; 13,85</t>
+          <t>2,57; 14,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,61; 13,57</t>
+          <t>2,49; 12,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,96; 21,01</t>
+          <t>8,9; 21,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,07; 22,74</t>
+          <t>12,41; 23,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,8; 17,48</t>
+          <t>7,09; 18,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,26; 21,41</t>
+          <t>3,48; 21,51</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,4; 17,49</t>
+          <t>10,11; 17,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,63; 13,23</t>
+          <t>5,65; 13,06</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,7; 19,68</t>
+          <t>8,07; 20,02</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>14,29; 94,8</t>
+          <t>11,4; 100,34</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>12,12; 93,66</t>
+          <t>11,55; 88,8</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>44,31; 145,43</t>
+          <t>42,59; 156,38</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>37,26; 86,51</t>
+          <t>38,67; 89,31</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>21,59; 67,26</t>
+          <t>21,47; 68,36</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,29; 80,45</t>
+          <t>13,06; 80,38</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,54; 77,75</t>
+          <t>37,73; 78,94</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>21,09; 57,51</t>
+          <t>21,09; 58,67</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>31,04; 86,96</t>
+          <t>32,8; 88,17</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 6,86</t>
+          <t>-1,69; 6,94</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 5,05</t>
+          <t>-2,68; 5,42</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 11,41</t>
+          <t>-0,94; 12,09</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7,79; 15,88</t>
+          <t>8,17; 16,2</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,44; 11,17</t>
+          <t>2,85; 11,19</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,81; 11,39</t>
+          <t>2,83; 11,61</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,36; 13,43</t>
+          <t>6,3; 13,65</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,13; 8,32</t>
+          <t>1,59; 8,75</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,2; 8,69</t>
+          <t>0,83; 8,55</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-29,21; 182,71</t>
+          <t>-29,72; 184,66</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-39,5; 140,24</t>
+          <t>-37,57; 152,64</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-28,62; 256,7</t>
+          <t>-17,75; 312,38</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>20,05; 45,82</t>
+          <t>21,4; 46,72</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>6,69; 32,96</t>
+          <t>7,47; 32,63</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,45; 33,35</t>
+          <t>7,57; 33,72</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,35; 47,34</t>
+          <t>19,5; 47,1</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3,8; 29,21</t>
+          <t>4,5; 30,02</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3,67; 29,62</t>
+          <t>2,66; 29,48</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>5,92; 9,99</t>
+          <t>5,72; 9,8</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3,62; 7,55</t>
+          <t>3,63; 7,71</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3,97; 13,48</t>
+          <t>4,44; 13,35</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7,65; 12,31</t>
+          <t>7,9; 12,61</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,59; 7,29</t>
+          <t>2,62; 7,49</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,27; 24,2</t>
+          <t>9,26; 24,12</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,29; 10,53</t>
+          <t>7,49; 10,55</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3,79; 6,9</t>
+          <t>3,64; 6,68</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>8,49; 17,91</t>
+          <t>8,61; 18,3</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>31,87; 60,54</t>
+          <t>30,89; 59,75</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>19,96; 46,73</t>
+          <t>19,2; 46,7</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>24,51; 80,3</t>
+          <t>27,22; 79,19</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>25,01; 42,88</t>
+          <t>25,64; 44,21</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>8,36; 25,8</t>
+          <t>8,42; 26,46</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>30,71; 81,4</t>
+          <t>30,52; 82,53</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,78; 45,9</t>
+          <t>30,62; 45,97</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>15,4; 30,07</t>
+          <t>14,84; 29,06</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>35,12; 76,65</t>
+          <t>35,09; 76,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A_n_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A_n_R2-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11,27</t>
+          <t>11,17</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,53</t>
+          <t>8,14</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10,46</t>
+          <t>10,23</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 10,24</t>
+          <t>-1,45; 9,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 11,22</t>
+          <t>-0,02; 11,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,03; 16,74</t>
+          <t>6,0; 16,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 9,72</t>
+          <t>-4,81; 9,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 5,11</t>
+          <t>-7,71; 5,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 14,06</t>
+          <t>1,91; 13,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 8,03</t>
+          <t>-0,44; 7,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 6,76</t>
+          <t>-1,2; 6,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,81; 14,44</t>
+          <t>6,05; 14,12</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>53,6%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 71,92</t>
+          <t>-8,25; 66,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 81,46</t>
+          <t>0,17; 83,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,95; 115,53</t>
+          <t>31,08; 115,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,46; 49,35</t>
+          <t>-18,74; 45,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-27,16; 27,81</t>
+          <t>-29,51; 28,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 75,0</t>
+          <t>6,25; 71,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 47,6</t>
+          <t>-2,09; 45,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 39,25</t>
+          <t>-5,77; 38,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,11; 84,83</t>
+          <t>27,1; 84,1</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13,04</t>
+          <t>13,05</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,74</t>
+          <t>9,2</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11,11</t>
+          <t>10,92</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 12,55</t>
+          <t>1,4; 12,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,78; 14,38</t>
+          <t>2,96; 14,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,61; 18,75</t>
+          <t>7,14; 18,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 12,25</t>
+          <t>-1,72; 12,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 7,39</t>
+          <t>-5,11; 7,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 15,6</t>
+          <t>3,14; 14,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 9,98</t>
+          <t>0,84; 9,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 8,89</t>
+          <t>0,33; 8,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,14; 14,89</t>
+          <t>6,88; 14,92</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>58,7%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 107,29</t>
+          <t>7,5; 114,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,54; 126,67</t>
+          <t>18,37; 125,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45,7; 169,97</t>
+          <t>39,88; 164,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 61,49</t>
+          <t>-8,04; 59,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,04; 36,55</t>
+          <t>-20,07; 37,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,29; 76,8</t>
+          <t>11,57; 72,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,07; 58,7</t>
+          <t>4,08; 57,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 53,02</t>
+          <t>1,69; 53,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,58; 90,73</t>
+          <t>31,9; 89,56</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,99</t>
+          <t>14,91</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,22</t>
+          <t>24,39</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7,87</t>
+          <t>18,07</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,65; 18,58</t>
+          <t>8,47; 18,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,55; 13,72</t>
+          <t>3,61; 13,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,54; 17,68</t>
+          <t>9,82; 19,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 18,74</t>
+          <t>1,7; 19,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 23,18</t>
+          <t>1,55; 22,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,95; 34,17</t>
+          <t>14,94; 33,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,12; 17,06</t>
+          <t>8,61; 17,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,9; 14,18</t>
+          <t>4,8; 13,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 20,29</t>
+          <t>13,45; 22,73</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>92,61%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44,13; 121,96</t>
+          <t>42,92; 125,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17,55; 90,52</t>
+          <t>18,87; 89,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-59,32; 106,64</t>
+          <t>50,29; 133,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,35; 86,43</t>
+          <t>4,87; 86,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,55; 105,16</t>
+          <t>4,32; 101,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48,29; 160,33</t>
+          <t>46,12; 161,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,06; 99,76</t>
+          <t>39,14; 100,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22,4; 80,64</t>
+          <t>23,43; 81,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-37,09; 108,47</t>
+          <t>62,01; 131,39</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12,96</t>
+          <t>12,86</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,26</t>
+          <t>12,12</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>19,47</t>
+          <t>12,83</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,71; 10,91</t>
+          <t>3,97; 11,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 6,5</t>
+          <t>-0,44; 6,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,25; 17,25</t>
+          <t>9,19; 16,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,04; 11,97</t>
+          <t>2,75; 12,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 5,83</t>
+          <t>-4,1; 5,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,78; 45,24</t>
+          <t>7,52; 16,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,75; 10,38</t>
+          <t>4,28; 10,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 5,15</t>
+          <t>-0,25; 5,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,02; 37,68</t>
+          <t>10,08; 15,83</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>55,14%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,45; 54,08</t>
+          <t>17,08; 53,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 32,18</t>
+          <t>-1,96; 32,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38,84; 81,99</t>
+          <t>39,76; 82,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,25; 50,71</t>
+          <t>8,62; 51,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-12,8; 24,5</t>
+          <t>-13,95; 23,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,64; 188,26</t>
+          <t>25,6; 68,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,9; 47,63</t>
+          <t>17,82; 46,81</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 23,38</t>
+          <t>-0,99; 24,36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>50,43; 169,03</t>
+          <t>40,42; 72,96</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15,44</t>
+          <t>13,47</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,62</t>
+          <t>19,15</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>15,15</t>
+          <t>16,56</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,57; 14,19</t>
+          <t>2,05; 13,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,49; 12,75</t>
+          <t>2,42; 12,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,9; 21,83</t>
+          <t>7,82; 19,06</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,41; 23,28</t>
+          <t>12,24; 23,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,09; 18,07</t>
+          <t>7,05; 17,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,48; 21,51</t>
+          <t>14,31; 23,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,11; 17,71</t>
+          <t>10,14; 17,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,65; 13,06</t>
+          <t>5,58; 13,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8,07; 20,02</t>
+          <t>12,66; 20,37</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>67,3%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>11,4; 100,34</t>
+          <t>9,78; 93,3</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>11,55; 88,8</t>
+          <t>11,78; 86,62</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>42,59; 156,38</t>
+          <t>35,21; 127,18</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>38,67; 89,31</t>
+          <t>37,64; 88,66</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>21,47; 68,36</t>
+          <t>21,77; 67,76</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,06; 80,38</t>
+          <t>44,58; 92,66</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,73; 78,94</t>
+          <t>37,48; 82,25</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>21,09; 58,67</t>
+          <t>21,7; 61,56</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>32,8; 88,17</t>
+          <t>46,79; 93,22</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4,03</t>
+          <t>4,75</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,17</t>
+          <t>6,06</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4,96</t>
+          <t>4,95</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 6,94</t>
+          <t>-1,9; 6,79</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 5,42</t>
+          <t>-2,81; 5,21</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 12,09</t>
+          <t>-0,46; 13,04</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8,17; 16,2</t>
+          <t>7,8; 16,31</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,85; 11,19</t>
+          <t>2,85; 11,21</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,83; 11,61</t>
+          <t>2,01; 10,26</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,3; 13,65</t>
+          <t>6,31; 13,3</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,59; 8,75</t>
+          <t>1,6; 8,79</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,83; 8,55</t>
+          <t>1,24; 8,67</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-29,72; 184,66</t>
+          <t>-27,4; 181,36</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-37,57; 152,64</t>
+          <t>-39,64; 140,46</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-17,75; 312,38</t>
+          <t>-12,7; 310,23</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>21,4; 46,72</t>
+          <t>19,73; 46,64</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7,47; 32,63</t>
+          <t>7,52; 32,45</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,57; 33,72</t>
+          <t>5,18; 29,4</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>19,5; 47,1</t>
+          <t>19,87; 45,96</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4,5; 30,02</t>
+          <t>4,89; 30,56</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2,66; 29,48</t>
+          <t>4,04; 30,64</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10,51</t>
+          <t>12,4</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,63</t>
+          <t>10,68</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>12,19</t>
+          <t>11,58</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>5,72; 9,8</t>
+          <t>5,82; 9,68</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3,63; 7,71</t>
+          <t>3,29; 7,41</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4,44; 13,35</t>
+          <t>10,32; 14,61</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7,9; 12,61</t>
+          <t>8,03; 12,66</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,62; 7,49</t>
+          <t>2,77; 7,48</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,26; 24,12</t>
+          <t>8,73; 13,03</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,49; 10,55</t>
+          <t>7,44; 10,6</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3,64; 6,68</t>
+          <t>3,77; 6,89</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>8,61; 18,3</t>
+          <t>10,05; 13,18</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>48,84%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>30,89; 59,75</t>
+          <t>31,49; 58,59</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>19,2; 46,7</t>
+          <t>17,88; 45,25</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>27,22; 79,19</t>
+          <t>56,15; 88,52</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>25,64; 44,21</t>
+          <t>26,19; 44,73</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>8,42; 26,46</t>
+          <t>8,92; 26,25</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>30,52; 82,53</t>
+          <t>27,9; 45,15</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>30,62; 45,97</t>
+          <t>30,51; 46,1</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>14,84; 29,06</t>
+          <t>15,41; 30,33</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>35,09; 76,54</t>
+          <t>40,97; 57,35</t>
         </is>
       </c>
     </row>
